--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\generador_certificados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03B1EA8-5C68-41BD-ABF7-07721A2F458A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CE7B6E-3918-4783-87F8-A45BC545EDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="560">
   <si>
     <t>Nombre</t>
   </si>
@@ -33,10 +33,1678 @@
     <t>DNI</t>
   </si>
   <si>
-    <t>MARCELO</t>
-  </si>
-  <si>
-    <t>nestor</t>
+    <t>ALFREDO LUIS NUÑEZ</t>
+  </si>
+  <si>
+    <t>MARIO FABIAN MONARDEZ</t>
+  </si>
+  <si>
+    <t>SILVIA MARY MALDONADO</t>
+  </si>
+  <si>
+    <t>MARIA GABRIELA DOMINGUEZ RUIZ</t>
+  </si>
+  <si>
+    <t>MARIA JOSE PELLICE AGUILERA</t>
+  </si>
+  <si>
+    <t>HILDA DEL CARMEN RUBIÑO</t>
+  </si>
+  <si>
+    <t>VERONICA MARCELA VILLEGA</t>
+  </si>
+  <si>
+    <t>ROBERTO DANIEL ALVAREZ ZURLO</t>
+  </si>
+  <si>
+    <t>MARIA CAROLINA NOTARIO</t>
+  </si>
+  <si>
+    <t>MONICA ELIANA PADILLA TRONCOSO</t>
+  </si>
+  <si>
+    <t>MARIANA GIAVARINI</t>
+  </si>
+  <si>
+    <t>SARA MARIA ALBAGLI</t>
+  </si>
+  <si>
+    <t>ETEL MAGALÍ BARBOZA</t>
+  </si>
+  <si>
+    <t>VERONICA BEATRIZ GUTIERREZ CUMPIAN</t>
+  </si>
+  <si>
+    <t>JAVIER SALVADOR PES CHIAVASSA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL BUENO VILLEGAS</t>
+  </si>
+  <si>
+    <t>JORGELINA BELEN PUERTA</t>
+  </si>
+  <si>
+    <t>MARÍA CRISTINA ABAD SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARIANA CECILIA FERRER</t>
+  </si>
+  <si>
+    <t>MARTIN NICOLAS DELGADO SALAZAR</t>
+  </si>
+  <si>
+    <t>VANESA PAULA BUSTOS FLORES</t>
+  </si>
+  <si>
+    <t>JULIAN ABEL TEJADA CASTILLO</t>
+  </si>
+  <si>
+    <t>RODRIGO EMANUEL VERA</t>
+  </si>
+  <si>
+    <t>MAYRA ANDREA SANTANDER MUÑOZ</t>
+  </si>
+  <si>
+    <t>CECILIA PAMELA ROMERO CARPIO</t>
+  </si>
+  <si>
+    <t>FRANCO MARIANO GONZALEZ</t>
+  </si>
+  <si>
+    <t>AGUERO MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>PEREYRA MARCELO AGUSTIN</t>
+  </si>
+  <si>
+    <t>OLGUIN AGUSTIN</t>
+  </si>
+  <si>
+    <t>CASTRO GAMEZ SUSANA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>GALLARDO ALICIA SILVANA</t>
+  </si>
+  <si>
+    <t>ALVAREZ ALEJANDRA EDITH</t>
+  </si>
+  <si>
+    <t>VARGAS ANDREA DIOLINDA</t>
+  </si>
+  <si>
+    <t>MOLINA ANDREA YANINA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ ESPIN ANDREA CAROLINA</t>
+  </si>
+  <si>
+    <t>CLEVERS ALE ANDREA NOELIA</t>
+  </si>
+  <si>
+    <t>PEREYRA ANDRES MAXIMILIANO</t>
+  </si>
+  <si>
+    <t>CARRIZO ANDREA LORENA</t>
+  </si>
+  <si>
+    <t>QUINTEROS ANDREA FAVIOLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ GUSTAVO ARIEL</t>
+  </si>
+  <si>
+    <t>FERNANDEZ AYELEN RUTH</t>
+  </si>
+  <si>
+    <t>MOYANO SOLEDAD BELEN</t>
+  </si>
+  <si>
+    <t>GARCIA CARINA GABRIELA</t>
+  </si>
+  <si>
+    <t>SILVA CARINA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>NAVEDA GOMEZ CARLA XIMENA</t>
+  </si>
+  <si>
+    <t>RUIZ CLAVEL CARLA JESUANA</t>
+  </si>
+  <si>
+    <t>GONZALEZ CHIFFEL CAROLINA ANABEL</t>
+  </si>
+  <si>
+    <t>AMAT MORALES CAROLINA INES</t>
+  </si>
+  <si>
+    <t>SILVA CAROLINA GABRIELA</t>
+  </si>
+  <si>
+    <t>PAEZ CAROLINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CASTELLINO MARIO EZEQUIEL</t>
+  </si>
+  <si>
+    <t>CECILIA GARCIA</t>
+  </si>
+  <si>
+    <t>BASTIAN MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>PIZARRO CECILIA LORENA</t>
+  </si>
+  <si>
+    <t>SANCHEZ CUMPIAN MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>MATUS CELIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>VEGA CLARA ELISABET</t>
+  </si>
+  <si>
+    <t>GIMENEZ CLAUDIA BEATRIZ</t>
+  </si>
+  <si>
+    <t>BARRERA CLAUDIO MAXIMILIANO</t>
+  </si>
+  <si>
+    <t>MUT VERONICA BEATRIZ</t>
+  </si>
+  <si>
+    <t>MOLINA DIAZ JUAN SIMÓN</t>
+  </si>
+  <si>
+    <t>ORTIZ CRISTIAN DANIEL</t>
+  </si>
+  <si>
+    <t>AGUIAR DANIEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>PUIGDOMENECH DANTE RAUL</t>
+  </si>
+  <si>
+    <t>PERZI ORLANDO DAVID</t>
+  </si>
+  <si>
+    <t>PEREZ DEBORAH DEL VALLE</t>
+  </si>
+  <si>
+    <t>HERRERO DIEGO LEONEL</t>
+  </si>
+  <si>
+    <t>PACHECO DUILIO JUAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHEGARAY MARIA FLORENCIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OROSCO EMILIO </t>
+  </si>
+  <si>
+    <t>FERNANDEZ EMILSE ROSANA</t>
+  </si>
+  <si>
+    <t>CASTRO FABIO ADRIAN</t>
+  </si>
+  <si>
+    <t>GODOY NAHUEL FACUNDO</t>
+  </si>
+  <si>
+    <t>FALCON TELLO CAROLINA GISELA</t>
+  </si>
+  <si>
+    <t>FELIX GEMA NOELIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDEZ CRISTHIAN MARIANO </t>
+  </si>
+  <si>
+    <t>PELLETIER FERNANDO JESUS</t>
+  </si>
+  <si>
+    <t>BALLATO GABRIELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>OLMOS CARLOS GASTON</t>
+  </si>
+  <si>
+    <t>CUMPIAN PASCUAL GEMINA VANESA</t>
+  </si>
+  <si>
+    <t>GINER HERRERO JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>TOBARES GISELA AYELEN</t>
+  </si>
+  <si>
+    <t>MORALES GRACIELA RAMONA</t>
+  </si>
+  <si>
+    <t>GUEVARA AGUDO DAYANA PAOLA</t>
+  </si>
+  <si>
+    <t>HEREDIA SUSANA DALINDA</t>
+  </si>
+  <si>
+    <t>GARCES MALDONADO MARIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>LISI FORCADA  MARÍA JOSÉ</t>
+  </si>
+  <si>
+    <t>JORQUERA JORGE ANGEL</t>
+  </si>
+  <si>
+    <t>CORTEZ LUNA JULIETA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>GONZALEZ MARIA JULIETA</t>
+  </si>
+  <si>
+    <t>NUÑEZ DIAZ KARINA MAGDALENA</t>
+  </si>
+  <si>
+    <t>NARVAEZ SILVANA NICOLASA ANDREA</t>
+  </si>
+  <si>
+    <t>NIEVAS MARIO ALBERTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENTEO LEANDRO </t>
+  </si>
+  <si>
+    <t>LUNA ESTELA LILIANA</t>
+  </si>
+  <si>
+    <t>MADRID LORENA MYRIAN</t>
+  </si>
+  <si>
+    <t>QUIROGA GOMEZ MARIA LORENA</t>
+  </si>
+  <si>
+    <t>CERCOS MABEL GRACIELA</t>
+  </si>
+  <si>
+    <t>TAPIAS VIVIANI MACARENA EVELIN</t>
+  </si>
+  <si>
+    <t>VERON MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ MARCELO CEFERINO</t>
+  </si>
+  <si>
+    <t>AGUIAR MARIA MARCELA</t>
+  </si>
+  <si>
+    <t>LOPEZ MARCELA CECILIA</t>
+  </si>
+  <si>
+    <t>TOLMOS CANCHALOSI MARCELO JAVIER</t>
+  </si>
+  <si>
+    <t>MENI GUTIERREZ MARCELO ANDRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZALAZAR  MARCELA </t>
+  </si>
+  <si>
+    <t>ARGÜELLO ENRIQUE MARIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>DIAZ MARIA LAURA</t>
+  </si>
+  <si>
+    <t>RIVEROS MARIA VICTORIA DEL VALLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIZUELA MARIO ALEJANDRO </t>
+  </si>
+  <si>
+    <t>PAREDES MARISOL JANET</t>
+  </si>
+  <si>
+    <t>REGALADO STELLA MARYS</t>
+  </si>
+  <si>
+    <t>MARRAS IVANA GLADIS</t>
+  </si>
+  <si>
+    <t>BILTES MATIAS JAVIER</t>
+  </si>
+  <si>
+    <t>SANCHEZ MAURO VICTOR</t>
+  </si>
+  <si>
+    <t>ORELLANO POBLETE ANDRES MAXIMILIANO</t>
+  </si>
+  <si>
+    <t>BAMONDI MELISA NOELIA</t>
+  </si>
+  <si>
+    <t>AGÜERO MELISA VICTORIA</t>
+  </si>
+  <si>
+    <t>GODOY SOLERNO MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ MORENO FEDERICO JESUS</t>
+  </si>
+  <si>
+    <t>MAYA MIGUEL ROBERTO</t>
+  </si>
+  <si>
+    <t>MINI SANSO CECILIA RAMONA</t>
+  </si>
+  <si>
+    <t>HIDALGO VILLARROEL MIRIAM VALERIA</t>
+  </si>
+  <si>
+    <t>DIAZ AIXA CORINA</t>
+  </si>
+  <si>
+    <t>AGUERO PLATERO NICOLAS ESTEBAN</t>
+  </si>
+  <si>
+    <t>MARTINEZ MORENO NADIA BELEN</t>
+  </si>
+  <si>
+    <t>OLMOS MARIA ARACELI</t>
+  </si>
+  <si>
+    <t>SAFFE MARTIN JORGE PABLO</t>
+  </si>
+  <si>
+    <t>LUCERO GARIPE AMALIA PAOLA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ HEREDIA PAULA MARIELA</t>
+  </si>
+  <si>
+    <t>YANADEL PEDRO MIGUEL</t>
+  </si>
+  <si>
+    <t>MALLEA PATRICIA LUCIA</t>
+  </si>
+  <si>
+    <t>PELAEZ ARIAS NORMA VIVIANA</t>
+  </si>
+  <si>
+    <t>LUNA HEREDIA JOSE JESUS</t>
+  </si>
+  <si>
+    <t>SPESO PABLO HORACIO</t>
+  </si>
+  <si>
+    <t>REYNA JORGE RAUL</t>
+  </si>
+  <si>
+    <t>BENIGNO PRISCILA EDITH</t>
+  </si>
+  <si>
+    <t>ALBARRACIN ALEJANDRA BARBARA</t>
+  </si>
+  <si>
+    <t>JUAN PABLO GARCIA GOMEZ</t>
+  </si>
+  <si>
+    <t>ORO WALTER ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ROMERO FLORES JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>TOBARES ALFREDO GASTON</t>
+  </si>
+  <si>
+    <t>LOPEZ ELIANA MAIRA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ ROBLEDO TATIANA MARIEL</t>
+  </si>
+  <si>
+    <t>PAEZ MARTIN OSVALDO</t>
+  </si>
+  <si>
+    <t>LOZADA ENRIQUE HORACIO</t>
+  </si>
+  <si>
+    <t>RAMIREZ GARCIA BLANCA ISABEL</t>
+  </si>
+  <si>
+    <t>PEREYRA RAUL NICOLAS</t>
+  </si>
+  <si>
+    <t>RIVEROS JORGE WILLIAMS</t>
+  </si>
+  <si>
+    <t>MADRID RODRIGO EDUARDO</t>
+  </si>
+  <si>
+    <t>GELVEZ MARTA ROSANA</t>
+  </si>
+  <si>
+    <t>GUERRERO SANDRA MARISA</t>
+  </si>
+  <si>
+    <t>MORENO PEÑA SERGIO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MAÑE SERGIO FABIAN</t>
+  </si>
+  <si>
+    <t>MUÑOZ SILVANA GRISELDA</t>
+  </si>
+  <si>
+    <t>GARCIA GARCIA SILVINA SALOMÉ</t>
+  </si>
+  <si>
+    <t>ROLDAN SONIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>TORRES STELLA MARIS</t>
+  </si>
+  <si>
+    <t>FERNANDEZ SILVIO RAUL</t>
+  </si>
+  <si>
+    <t>CUEVAS MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>TULA ELSA LIDIA</t>
+  </si>
+  <si>
+    <t>DIAZ VALERIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>AGUIRRE PRINGLES VERONICA FÁTIMA</t>
+  </si>
+  <si>
+    <t>VIDELA PEDROZO MELINA AYELEN</t>
+  </si>
+  <si>
+    <t>VILCHEZ MYRIAM ALICIA</t>
+  </si>
+  <si>
+    <t>MALDONADO AGUERO XIMENA DEL MILAGRO</t>
+  </si>
+  <si>
+    <t>MALLA YANINA ELIZABETH</t>
+  </si>
+  <si>
+    <t>PAEZ SARMIENTO JAQUELINA IVONNE</t>
+  </si>
+  <si>
+    <t>YAZMIN SOLANGE LEIVA URTUBIA</t>
+  </si>
+  <si>
+    <t>GARCIA ROSANA VERONICA</t>
+  </si>
+  <si>
+    <t>ZAPPALA MARCELO DARIO</t>
+  </si>
+  <si>
+    <t>VIDELA RODRÍGUEZ ABIGAIL GUADALUPE</t>
+  </si>
+  <si>
+    <t>LUCERO ADELA YANINA</t>
+  </si>
+  <si>
+    <t>GUZMAN GARCIA ADRIANA</t>
+  </si>
+  <si>
+    <t>GIMENEZ ADRIANA IRENE</t>
+  </si>
+  <si>
+    <t>MERCADO ADRIAN RICARDO</t>
+  </si>
+  <si>
+    <t>TORRES JAVIER ADRIAN</t>
+  </si>
+  <si>
+    <t>ROCO PELAEZ AGOSTINA MARISOL</t>
+  </si>
+  <si>
+    <t>GODOY PEREZ AGUSTINA NOEL</t>
+  </si>
+  <si>
+    <t>VIDABLE PAEZ MARIA AGUSTINA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ MARIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>OCAMPO ALEJANDRA MARIELA</t>
+  </si>
+  <si>
+    <t>LACIAR MARÍA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MOYA GUZMÁN NICOLÁS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MOLINA ALICIA BEATRÍZ</t>
+  </si>
+  <si>
+    <t>CABALLERO JOAQUIN HUMBERTO</t>
+  </si>
+  <si>
+    <t>VELARDEZ ANALIA MARIANA</t>
+  </si>
+  <si>
+    <t>ABOITIZ ANGELES</t>
+  </si>
+  <si>
+    <t>REINOSO ANALIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>MOLINA ANGEL RUBEN</t>
+  </si>
+  <si>
+    <t>CAMARGO MANSILLA BEATRIZ ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MORENO BERON OLGA GRACIELA</t>
+  </si>
+  <si>
+    <t>MENDEZ PABLO DARIO</t>
+  </si>
+  <si>
+    <t>CABRERA GIMENEZ VANESA ANTONIA</t>
+  </si>
+  <si>
+    <t>ALVAREZ CAROLINA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>CASTRO MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MONTAÑO GALDEANO MAURICIO JAVIER</t>
+  </si>
+  <si>
+    <t>CIANI CLAUDIA GRACIELA</t>
+  </si>
+  <si>
+    <t>MORELY CARLOS DANILO</t>
+  </si>
+  <si>
+    <t>MARTINEZ BEGUERI MARIA CELESTE</t>
+  </si>
+  <si>
+    <t>CORREA MARIA CELINA</t>
+  </si>
+  <si>
+    <t>HOGAZ AVILA CELINA BEATRIZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ CELINA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ZAGARRA CECILIA</t>
+  </si>
+  <si>
+    <t>PANTANO AGUIRRE CLAUDIO GUSTAVO</t>
+  </si>
+  <si>
+    <t>AGUERO CRISTIAN EZEQUIEL</t>
+  </si>
+  <si>
+    <t>LARIA RUEDA ANA CRISTINA</t>
+  </si>
+  <si>
+    <t>ORDINES ESCRIBÁ DANIELA MABEL</t>
+  </si>
+  <si>
+    <t>GUTIERREZ DANIELA NOEMÍ</t>
+  </si>
+  <si>
+    <t>LLORET VILDOSO ULISES DAVID</t>
+  </si>
+  <si>
+    <t>ALMARCHA SERAFINI DIEGO ALFREDO</t>
+  </si>
+  <si>
+    <t>SILVA VILDOZA DANIELA JULIETA</t>
+  </si>
+  <si>
+    <t>DURAN HERMOSO MARIA JULIETA</t>
+  </si>
+  <si>
+    <t>PEREZ MARTINEZ ESTEBAN EMILIANO</t>
+  </si>
+  <si>
+    <t>ALBORNOS CHIRINO ELIANA ANAHI</t>
+  </si>
+  <si>
+    <t>MACIAS EMANUEL EDUARDO</t>
+  </si>
+  <si>
+    <t>GARRIDO GOMEZ EMANUEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ASTUDILLO EMILIO GASTON</t>
+  </si>
+  <si>
+    <t>LEIVA PAZ MARIA EMILIA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ EMILIO ANDRÉS</t>
+  </si>
+  <si>
+    <t>MALDONADO RAMOS EMILSE GEMMA</t>
+  </si>
+  <si>
+    <t>CARRION CUBO VICTOR EMMANUEL</t>
+  </si>
+  <si>
+    <t>BARZOLA QUIROGA ERICA ELIZABETH</t>
+  </si>
+  <si>
+    <t>VEGA ERICA JACQUELINE</t>
+  </si>
+  <si>
+    <t>RAMON NAUMCHIK MARIA ESTHER</t>
+  </si>
+  <si>
+    <t>CHAPARRO FEMIA MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>RIVAS PALACIO MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOFRE HECTOR FACUNDO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ FACUNDO</t>
+  </si>
+  <si>
+    <t>RIVADENEIRA FRANCO DAVID</t>
+  </si>
+  <si>
+    <t>MUÑOZ BARRIOS FEDERICO LAUTARO</t>
+  </si>
+  <si>
+    <t>RAMIREZ AZURI MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MOYANO MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ FRANCO</t>
+  </si>
+  <si>
+    <t>FRIAS FABRICIO ORLANDO</t>
+  </si>
+  <si>
+    <t>PÁEZ PASTOR MARIA FLORENCIA</t>
+  </si>
+  <si>
+    <t>PINAVARIA LORENA MERCEDES</t>
+  </si>
+  <si>
+    <t>GIGENA GABRIELA EDITH</t>
+  </si>
+  <si>
+    <t>SAMAT GABRIEL DARÍO</t>
+  </si>
+  <si>
+    <t>CERDERA RODRIGUEZ GERARDO JOSÉ</t>
+  </si>
+  <si>
+    <t>FERNANDEZ MANINI GERARDO ANDRES</t>
+  </si>
+  <si>
+    <t>MARTINEZ RICARDO ARIEL</t>
+  </si>
+  <si>
+    <t>CARABALLO ROMINA GISELLE</t>
+  </si>
+  <si>
+    <t>MORANDI GISELA ELIANA</t>
+  </si>
+  <si>
+    <t>YACANTE GLORIA ALICIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ GRISEL RITA</t>
+  </si>
+  <si>
+    <t>SANCHEZ CEJAS GUSTAVO GABRIEL</t>
+  </si>
+  <si>
+    <t>GARCIA GUSTAVO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MORENO NOGUERA GUSTAVO ADRIAN</t>
+  </si>
+  <si>
+    <t>HARO SANCHEZ MILAGRO VICTORIA</t>
+  </si>
+  <si>
+    <t>GALVEZ HEBE ROSANA</t>
+  </si>
+  <si>
+    <t>MUÑOZ PALACIO INGRID GERALDINE</t>
+  </si>
+  <si>
+    <t>FLORES CARRIZO BLANCA JANET</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ RIVOLETTI JUAN DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>RIVERA JEFF EMANUEL</t>
+  </si>
+  <si>
+    <t>MENTESANO JÉSICA</t>
+  </si>
+  <si>
+    <t>GUARDIA MATAIX JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>PETIT JONATAN ARIEL</t>
+  </si>
+  <si>
+    <t>CORREA JUAN CRUZ</t>
+  </si>
+  <si>
+    <t>FERRUCCIO JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JUAREZ GONZALO</t>
+  </si>
+  <si>
+    <t>JACOME GONZALEZ JULIETA EMILCE</t>
+  </si>
+  <si>
+    <t>GRAMAJO JULIETA ELIZABETH</t>
+  </si>
+  <si>
+    <t>BIANCO REYES JULIETA MARIA</t>
+  </si>
+  <si>
+    <t>LOPARDO JULIETA LARA</t>
+  </si>
+  <si>
+    <t>DIAZ GARCIA MARIA LAURA</t>
+  </si>
+  <si>
+    <t>TRUJILLANO MARUN LUCIA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>PERALTA AVILA LEANDRO ISMAEL</t>
+  </si>
+  <si>
+    <t>MORENO ESTEBAN LEONARDO</t>
+  </si>
+  <si>
+    <t>ESPINOSA LETICIA BEATRIZ</t>
+  </si>
+  <si>
+    <t>LOPEZ BAWDEN FACUNDO NICOLAS</t>
+  </si>
+  <si>
+    <t>ELIAS LUCAS DAVID</t>
+  </si>
+  <si>
+    <t>LEIVA GALAS LUCAS GABRIEL</t>
+  </si>
+  <si>
+    <t>LUJAN JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>ROMERO CHICAHUALA LUZ MARIA</t>
+  </si>
+  <si>
+    <t>BEGUERI PERALTA MARCELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>GOMEZ MARCELA MONICA</t>
+  </si>
+  <si>
+    <t>AYLLON ARIAS MARCELO OMAR</t>
+  </si>
+  <si>
+    <t>CABALLERO MARCELO JAVIER</t>
+  </si>
+  <si>
+    <t>OLIVEROS MARCELO JAVIER</t>
+  </si>
+  <si>
+    <t>VERDU MARCOS EXEQUIEL</t>
+  </si>
+  <si>
+    <t>DOHMEN ARACENA MARIA ELINA</t>
+  </si>
+  <si>
+    <t>PALACIO SALVA MARIA LAURA</t>
+  </si>
+  <si>
+    <t>GONZALEZ VARGAS MARIANA LUZ</t>
+  </si>
+  <si>
+    <t>ESQUIVEL PUIGDOMENECH MARIANA AGUSTINA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ VALERO MARIANA</t>
+  </si>
+  <si>
+    <t>SANCHEZ DENIZ MARIANA NAIR</t>
+  </si>
+  <si>
+    <t>CARA CORTEZ MARIANELA</t>
+  </si>
+  <si>
+    <t>RAMIREZ MARIA SUSANA</t>
+  </si>
+  <si>
+    <t>MERIDA MARIO MARCELO</t>
+  </si>
+  <si>
+    <t>GIMENEZ CALISSE MARISA SILVANA</t>
+  </si>
+  <si>
+    <t>ORO GONZALEZ CARLOS MARTIN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ MARÍA SILVANA</t>
+  </si>
+  <si>
+    <t>CORDERO GORDILLO MATIAS LEONARDO</t>
+  </si>
+  <si>
+    <t>DEL CASTILLO MAURICIO NICOLAS</t>
+  </si>
+  <si>
+    <t>ESPEJO MAURO RICARDO</t>
+  </si>
+  <si>
+    <t>MIRANDA MAURICIO</t>
+  </si>
+  <si>
+    <t>VILLALOBOS MAYRA ANDREA</t>
+  </si>
+  <si>
+    <t>OVIEDO MAYRA AYELEN</t>
+  </si>
+  <si>
+    <t>DIAZ BALMACEDA MAYRA VICTORIA</t>
+  </si>
+  <si>
+    <t>VILLAVICENCIO CARBAJAL MAYRA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ MUÑOZ MARIA BELEN</t>
+  </si>
+  <si>
+    <t>NIEVAS MARIA CLAUDIA</t>
+  </si>
+  <si>
+    <t>TELLO MELISA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ARAMBURU GUTIERREZ MARIA ROMINA</t>
+  </si>
+  <si>
+    <t>ECHEGARAY MONICA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>VIVES MONICA GRACIELA</t>
+  </si>
+  <si>
+    <t>VERA MYRIAM VIVIANA</t>
+  </si>
+  <si>
+    <t>CHAQUERIAN NADIA SOLEDAD</t>
+  </si>
+  <si>
+    <t>HOGALDE GONZALEZ NAHUEL AGUSTÍN</t>
+  </si>
+  <si>
+    <t>LEUZZI NATALIA VERONICA</t>
+  </si>
+  <si>
+    <t>SALINAS PEREZ NATALIA GRACIELA</t>
+  </si>
+  <si>
+    <t>OSES MONTAUDO NICOLAS AGUSTIN</t>
+  </si>
+  <si>
+    <t>RIVAS NOGALÍ VIVIANA</t>
+  </si>
+  <si>
+    <t>BALMACEDA CARBAJAL NORA NATIVIDAD</t>
+  </si>
+  <si>
+    <t>VALENZUELA NORMA DEL VALLE</t>
+  </si>
+  <si>
+    <t>SULIGOY LOZANO MARIA NATALIA</t>
+  </si>
+  <si>
+    <t>PEREZ DESIRÉE</t>
+  </si>
+  <si>
+    <t>NIEVAS RAUL MARCELO</t>
+  </si>
+  <si>
+    <t>PERALTA MAURICIO DANIEL</t>
+  </si>
+  <si>
+    <t>ELIZONDO JUAN MARIA CELESTE</t>
+  </si>
+  <si>
+    <t>FLORES SEBASTIAN RAUL</t>
+  </si>
+  <si>
+    <t>GIMENEZ CORONADO EDUARDO FACUNDO</t>
+  </si>
+  <si>
+    <t>GARAY BUSTOS MARIA ELINA</t>
+  </si>
+  <si>
+    <t>VARAS ARROYO WALTER JESUS</t>
+  </si>
+  <si>
+    <t>PUIGGROS MARIA LUCIANA</t>
+  </si>
+  <si>
+    <t>COLLADO RAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>MARTIN BERTONI ROCIO MAGALI</t>
+  </si>
+  <si>
+    <t>PERALTA BAEZ ROMAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>VICTORIA NATALIA ROMINA</t>
+  </si>
+  <si>
+    <t>CORNEJO FERNANDEZ MIRTA ROSANA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SANCHEZ MARCELA ARGENTINA</t>
+  </si>
+  <si>
+    <t>ARAVENA DOMINGO FABIAN</t>
+  </si>
+  <si>
+    <t>SASO JORGE JAVIER</t>
+  </si>
+  <si>
+    <t>OLMOS OSCAR SEBASTIAN</t>
+  </si>
+  <si>
+    <t>MONTEVERDE SERENA</t>
+  </si>
+  <si>
+    <t>ROJO MARIA GABRIELA</t>
+  </si>
+  <si>
+    <t>VILANOVA LOPEZ SANDRA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>GALLO MARIA TERESITA BELEN</t>
+  </si>
+  <si>
+    <t>BECERRA FRAIFER LILIANA VANESA</t>
+  </si>
+  <si>
+    <t>BOTAS RIPOLL VANINA MARILIN</t>
+  </si>
+  <si>
+    <t>GONZALEZ VIVIANA DEOLINDA</t>
+  </si>
+  <si>
+    <t>MAS PINTO MARIA VICTORIA</t>
+  </si>
+  <si>
+    <t>ORMEÑO VICTOR DAVID</t>
+  </si>
+  <si>
+    <t>LARIA VIVIANA EDITH</t>
+  </si>
+  <si>
+    <t>BALMACEDA IBAZETA MARIA YANINA</t>
+  </si>
+  <si>
+    <t>MADRID YANINA ELIZABETH</t>
+  </si>
+  <si>
+    <t>RIVAS BRIZUELA YESICA NATALI</t>
+  </si>
+  <si>
+    <t>ERNESTO RODOLFO SOLAR</t>
+  </si>
+  <si>
+    <t>MAURICIO JAVIER ORTIZ BALMACEDA</t>
+  </si>
+  <si>
+    <t>ROBERTO GUSTAVO CUEVA GARCÍA</t>
+  </si>
+  <si>
+    <t>FERNANDO GABRIEL CUEVA</t>
+  </si>
+  <si>
+    <t>GONZALO JAVIER FIGUEROA</t>
+  </si>
+  <si>
+    <t>EBERTO MAXIMILIANO PARADA</t>
+  </si>
+  <si>
+    <t>JUAN ESTEBAN RODRIGUEZ PÁEZ</t>
+  </si>
+  <si>
+    <t>LEONARDO ALBERTO FARA</t>
+  </si>
+  <si>
+    <t>NICOLAS CESAR QUIROGA JOFRE</t>
+  </si>
+  <si>
+    <t>JORGE DANIEL ARNAEZ FIGUEROA</t>
+  </si>
+  <si>
+    <t>HUGO ARMANDO AGUIRRE</t>
+  </si>
+  <si>
+    <t>NICOLE CUEVA PALACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAN ENZO MONTAÑA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRENDAA MARIA EVA BRIZUELA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFIA MAILEN AGUADO </t>
+  </si>
+  <si>
+    <t>SOFIA ARIANA SALINA MARINERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATIAS EMANUEL CABALLERO </t>
+  </si>
+  <si>
+    <t>FRANCISCO BENICIO CRUZ AGUILERA MUÑOZ</t>
+  </si>
+  <si>
+    <t>CRISTAN ARIEL MANRIQUE ESPEJO</t>
+  </si>
+  <si>
+    <t>JANET AYELEN VEDIA ILLANES</t>
+  </si>
+  <si>
+    <t>JUAN IGNACIO DIAZ</t>
+  </si>
+  <si>
+    <t>PABLO DIONICIO BARRIOS RAMOS</t>
+  </si>
+  <si>
+    <t>LUCASA LEJANDRO MANTAÑA CARTILLO</t>
+  </si>
+  <si>
+    <t>LAUTARO  MARTIN RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARIADNA LUJAN EQUIVEL</t>
+  </si>
+  <si>
+    <t>LUCAS AGUSTIN ESPEJO PARADA</t>
+  </si>
+  <si>
+    <t>JONAS LAUTARO MUÑOZ</t>
+  </si>
+  <si>
+    <t>CRISTINA MARIA AGÜERO RIVEROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIAN MAXIMILIANO PAREDES </t>
+  </si>
+  <si>
+    <t>GONZALO JUAN LAKA QUISPE</t>
+  </si>
+  <si>
+    <t>MARCELO GABRIEL PEREZ VILLALVA</t>
+  </si>
+  <si>
+    <t>LUCIANA MICAELA AGUERO</t>
+  </si>
+  <si>
+    <t>ROSA ALEXANDRA ALBARRACIN</t>
+  </si>
+  <si>
+    <t>MARÍA ANGELA GARCÍA</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES BACA ADARO</t>
+  </si>
+  <si>
+    <t>MARIA VICTORIA BERON</t>
+  </si>
+  <si>
+    <t>DANIELA ALEJANDRA TEJADA AVARCA</t>
+  </si>
+  <si>
+    <t>FRANCO DANTE CALIVA</t>
+  </si>
+  <si>
+    <t>GIMENA NATALIA VERA</t>
+  </si>
+  <si>
+    <t>IRIS NATALIA CASTRO</t>
+  </si>
+  <si>
+    <t>LAURA ANDREA VEDIA</t>
+  </si>
+  <si>
+    <t>FRANCO MAXIMILIANO PAEZ ILLANES</t>
+  </si>
+  <si>
+    <t>ROSA ELENA PAEZ</t>
+  </si>
+  <si>
+    <t>RODRIGO OMAR FERREYRA RUBIA</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARIEL ROSALES VEDIA</t>
+  </si>
+  <si>
+    <t>VIOLETA DEL VALLE LUNA</t>
+  </si>
+  <si>
+    <t>ROSARIO ELIZABETH SERRANO</t>
+  </si>
+  <si>
+    <t>CARLOS JOSE MANUEL DIAZ RIPOLL</t>
+  </si>
+  <si>
+    <t>MARIA GABRIELA NICOLIA MORALES</t>
+  </si>
+  <si>
+    <t>ANDREA GISELA VILLAFAÑE</t>
+  </si>
+  <si>
+    <t>PABLO SEBASTIAN PAEZ</t>
+  </si>
+  <si>
+    <t>MARIA ANDREA MERCADO</t>
+  </si>
+  <si>
+    <t>ROBERTO CARLOS GONZALES</t>
+  </si>
+  <si>
+    <t>DAMIAN CONTRERAS</t>
+  </si>
+  <si>
+    <t>GUSTAVO ARIEL SAAVEDRA VEGA</t>
+  </si>
+  <si>
+    <t>RICARDO DANIEL IBAZETA</t>
+  </si>
+  <si>
+    <t>BRIAN DIDIER IBAZETA RAMIREZ</t>
+  </si>
+  <si>
+    <t>EMILIO DANIEL CHAPARRO</t>
+  </si>
+  <si>
+    <t>GASTON KEVIN TAPIA PEREZ</t>
+  </si>
+  <si>
+    <t>JULIETA MICAELA  MEDRANO</t>
+  </si>
+  <si>
+    <t>ELUNEY ETEL JOFRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALIA DEL VALLE ASTUDILLO                                                                </t>
+  </si>
+  <si>
+    <t>GUILLERMO DAVID ABALLAY</t>
+  </si>
+  <si>
+    <t>JORGE ELENIO SUAREZ LUCERO</t>
+  </si>
+  <si>
+    <t>ABEL AQUILES VERA SAAVEDRA</t>
+  </si>
+  <si>
+    <t>ADRIANA VIVIANA KATARINIC</t>
+  </si>
+  <si>
+    <t>AGUSTIN OLGUIN</t>
+  </si>
+  <si>
+    <t>ALBA LINA OLGUIN</t>
+  </si>
+  <si>
+    <t>ANA LAURA SANCHEZ LOPEZ</t>
+  </si>
+  <si>
+    <t>ANALÍA NOEMÍ MOLINA</t>
+  </si>
+  <si>
+    <t>BRUNO OSCAR MONTILLA</t>
+  </si>
+  <si>
+    <t>CARLA JESUANA RUIZ CLAVEL</t>
+  </si>
+  <si>
+    <t>CARLOS FACUNDO SUAREZ GUTIERREZ</t>
+  </si>
+  <si>
+    <t>CAROLINA FLORENCIA BALMACEDA MAYER</t>
+  </si>
+  <si>
+    <t>CECILIA INES PEREZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CHRISTIAN EMANUEL MONTION</t>
+  </si>
+  <si>
+    <t>CINTHIA MARIANA HUERTAS</t>
+  </si>
+  <si>
+    <t>CLAUDIA IVANA FEMENIA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PATRICIA CERCOS CANO</t>
+  </si>
+  <si>
+    <t>ENZO GABRIEL DEIANA QUIROGA</t>
+  </si>
+  <si>
+    <t>FABRIZZIO RICARDO ALVAREZ</t>
+  </si>
+  <si>
+    <t>FATIMA MABEL QUINTERO GARCIA</t>
+  </si>
+  <si>
+    <t>FEDERICO LEONARDO PELAYES GUTIERREZ</t>
+  </si>
+  <si>
+    <t>FLAVIO GASTON DE LA VEGA</t>
+  </si>
+  <si>
+    <t>FLORENCIA AGOSTINA BAUDONNET IBAÑEZ</t>
+  </si>
+  <si>
+    <t>GONZALO EMILIANO VEGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRACIELA NOELIA ALAMEDA </t>
+  </si>
+  <si>
+    <t>GUADALUPE ESCRIBÁ</t>
+  </si>
+  <si>
+    <t>IVAN EMANUEL ILLANES VARAZA</t>
+  </si>
+  <si>
+    <t>IVANA GLADIS MARRAS</t>
+  </si>
+  <si>
+    <t>JOHANA MARLENE ARGUMOZA</t>
+  </si>
+  <si>
+    <t>JORGE ELIAS BALMACEDA CHAPARRO</t>
+  </si>
+  <si>
+    <t>JORGE JAVIER NARVAEZ MAS</t>
+  </si>
+  <si>
+    <t>LAURA ANDREA CARRATU</t>
+  </si>
+  <si>
+    <t>LEILA TATIANA LEZCANO LEIVA</t>
+  </si>
+  <si>
+    <t>MARCELO ANTONIO RUIZ</t>
+  </si>
+  <si>
+    <t>MARIA ELENA CARRIZO</t>
+  </si>
+  <si>
+    <t>MARIA GABRIELA POSATINI PARRA</t>
+  </si>
+  <si>
+    <t>MARIA INES ACOSTA</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL GENOVART</t>
+  </si>
+  <si>
+    <t>MARIANA BELEN LEZCANO LEIVA</t>
+  </si>
+  <si>
+    <t>MARIANA SEPULVEDA ESCUDERO</t>
+  </si>
+  <si>
+    <t>MARIO NICOLÁS DIAZ</t>
+  </si>
+  <si>
+    <t>MARTIN ALEJANDRO NOGUERA CAMUÑAS</t>
+  </si>
+  <si>
+    <t>MAURO ANDRES VERA SAAVEDRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELANIE DEL CARMEN PINTO </t>
+  </si>
+  <si>
+    <t>MONICA VIDELA</t>
+  </si>
+  <si>
+    <t>NANCY BENITA RODRIGUEZ GUILLEN</t>
+  </si>
+  <si>
+    <t>NEREA ROXANA GUALLAMA SABAS</t>
+  </si>
+  <si>
+    <t>PABLO MAURICIO SOSA</t>
+  </si>
+  <si>
+    <t>PATRICIA ELIZABETH ASTUDILLO IBACETA</t>
+  </si>
+  <si>
+    <t>RAÚL ALBERTO PEREZ</t>
+  </si>
+  <si>
+    <t>RAUL ALBERTO ZEBALLOS</t>
+  </si>
+  <si>
+    <t>RICARDO ANTONIO ARMANDO OCAÑA VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>RICARDO GERMAN MEDINA FERRER</t>
+  </si>
+  <si>
+    <t>ROBERTO ALEJANDRO SIERRA MARCUZZI</t>
+  </si>
+  <si>
+    <t>ROCÍO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RODOLFO ERNESTO MADRID</t>
+  </si>
+  <si>
+    <t>RODOLFO HIDALGO</t>
+  </si>
+  <si>
+    <t>ROMINA PAOLA GAVILA</t>
+  </si>
+  <si>
+    <t>ROSA MORENO</t>
+  </si>
+  <si>
+    <t>RUBEN DARIO LEONARDI</t>
+  </si>
+  <si>
+    <t>SAIDA NOEMI SIDEROL GODOY</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN LIMA</t>
+  </si>
+  <si>
+    <t>SERGIO FABIAN MAÑE</t>
+  </si>
+  <si>
+    <t>VERÒNICA SILVANA GODOY ADARO</t>
+  </si>
+  <si>
+    <t>WILSON DANIEL CORREA</t>
+  </si>
+  <si>
+    <t>FERNANDO ARIEL CARBAJAL</t>
+  </si>
+  <si>
+    <t>YAMIL LEONARDO MUÑOZ LUNA</t>
+  </si>
+  <si>
+    <t>ANDRÉS ANIBAL GELVEZ</t>
+  </si>
+  <si>
+    <t>GRACIELA INES ACIAR</t>
+  </si>
+  <si>
+    <t>ANA MARIA BRIZULA MONTIVERO</t>
+  </si>
+  <si>
+    <t>ANABEL COSTA SANCHEZ</t>
+  </si>
+  <si>
+    <t>DANIEL WALDO COSTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVID OSCAR ELIZONDO </t>
+  </si>
+  <si>
+    <t>JESSICA GUNELLA</t>
+  </si>
+  <si>
+    <t>JOSÉ MANUEL GUERRERO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS COSTA</t>
+  </si>
+  <si>
+    <t>RUBEN DARIO LECAM</t>
+  </si>
+  <si>
+    <t>GUSTAVO MARTIN VILLAFAÑE FLORES</t>
+  </si>
+  <si>
+    <t>NOEMI SOLER</t>
+  </si>
+  <si>
+    <t>PABLO CRISTIAN ELIZONDO ESCOBAL</t>
+  </si>
+  <si>
+    <t>PAULO MAURICIO VERA AGÜERO</t>
+  </si>
+  <si>
+    <t>PILAR LOPEZ</t>
+  </si>
+  <si>
+    <t>RAUL RICARDO IBACETA</t>
+  </si>
+  <si>
+    <t>JAVIER RUBEN ONTIVEROS</t>
+  </si>
+  <si>
+    <t>SILVINA VANESA TEJADA</t>
+  </si>
+  <si>
+    <t>YAMILA ESTEFANÍA GALLEGUILLO ROMERO</t>
+  </si>
+  <si>
+    <t>IVANA BEATRIZ CORTEZ</t>
+  </si>
+  <si>
+    <t>ROLANDO EMANUEL SALDIVAR OZAN</t>
+  </si>
+  <si>
+    <t>MARCELA ALEJANDRA GOMEZ</t>
+  </si>
+  <si>
+    <t>MARTIN JOSE LUNA AHUMADA</t>
+  </si>
+  <si>
+    <t>LAURA MABEL ROJAS</t>
+  </si>
+  <si>
+    <t>ROCIO DEL CARMEN PEÑALOZA</t>
+  </si>
+  <si>
+    <t>BEATRIZ SUSANA FERNANDEZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>CAMILA FLORES MASCARELL</t>
+  </si>
+  <si>
+    <t>LEONARDO DANIEL ORTIZ CALDERON</t>
+  </si>
+  <si>
+    <t>LORENA VERONICA SCARDINO</t>
+  </si>
+  <si>
+    <t>MARIA CRISTINA ALONZO</t>
+  </si>
+  <si>
+    <t>VANESA CARINA GONZALEZ</t>
+  </si>
+  <si>
+    <t>CECILIA ELENA MINI LOPEZ</t>
+  </si>
+  <si>
+    <t>DEOLINDA ESTELA DOMÍNGUEZ</t>
+  </si>
+  <si>
+    <t>RUBEN ARIEL MORAN</t>
+  </si>
+  <si>
+    <t>LEONARDO GASTON PEREYRA CASTRO</t>
+  </si>
+  <si>
+    <t>MARIA BELEN FERNANDEZ</t>
+  </si>
+  <si>
+    <t>CLAUDIA NOEMI YACANTE</t>
+  </si>
+  <si>
+    <t>MELISA ANDREA MORALES</t>
+  </si>
+  <si>
+    <t>DELIA ALICIA GODOY</t>
+  </si>
+  <si>
+    <t>JOSE IGNACIO BONILLA MACHUCA</t>
+  </si>
+  <si>
+    <t>GABRIELA RAQUEL GUZMAN GONZALEZ</t>
+  </si>
+  <si>
+    <t>MABEL ELIA RIOS</t>
+  </si>
+  <si>
+    <t>MAURO DANIEL QUIROGA LEYES</t>
+  </si>
+  <si>
+    <t>SILVANA EDITH CUADRADO</t>
+  </si>
+  <si>
+    <t>MARIA CELESTE LUNA LOPEZ</t>
+  </si>
+  <si>
+    <t>ZAIDA NIDIA AGÜERO NARANJO</t>
+  </si>
+  <si>
+    <t>ALEXIS NOEL BRITO</t>
+  </si>
+  <si>
+    <t>MARIA ANTONIA HERRERA</t>
+  </si>
+  <si>
+    <t>STELLA MARIS VARGAS</t>
+  </si>
+  <si>
+    <t>SILVIA NATALIA DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>PABLO GABRIEL DIAZ</t>
+  </si>
+  <si>
+    <t>MARIA ANDREA JOFRE</t>
+  </si>
+  <si>
+    <t>MARTIN MARCOS QUIROGA LEYES</t>
+  </si>
+  <si>
+    <t>XIMENA NATACHA RODRIGUEZ LUQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARINA ROSANA SANCHEZ </t>
+  </si>
+  <si>
+    <t>PAMELA VICENTA NIEVAS</t>
+  </si>
+  <si>
+    <t>ADRÍAN DAVID ROJAS ACUÑA</t>
+  </si>
+  <si>
+    <t>ELIZABETH ALEJANDRA DE FÁTIMA PEREZ</t>
+  </si>
+  <si>
+    <t>JULIETA ESCUDERO FERNANDEZ</t>
+  </si>
+  <si>
+    <t>NADIA ELIZABETH GALVEZ</t>
+  </si>
+  <si>
+    <t>MARIO JESUS VARGAS RIVERO</t>
+  </si>
+  <si>
+    <t>ALEJANDRA GEMA MOYA</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS LUCERO</t>
+  </si>
+  <si>
+    <t>DIEGO ANDRÉS VELASCO GRGIC</t>
+  </si>
+  <si>
+    <t>AMELIA YAEL APEZ CHIRINO</t>
+  </si>
+  <si>
+    <t>EDUARDO ENRIQUE PASTRAN</t>
+  </si>
+  <si>
+    <t>NÉLIDA RAQUEL DIAZ</t>
+  </si>
+  <si>
+    <t>WALTER ESEQUIEL FERNANDEZ ROLDAN</t>
+  </si>
+  <si>
+    <t>STELLA MARIS ORIZ POBLETE</t>
+  </si>
+  <si>
+    <t>ROMINA BERENGUER PERALTA</t>
+  </si>
+  <si>
+    <t>DEBORA MARCELA ECHENIQUE</t>
+  </si>
+  <si>
+    <t>MARIA LAURA SEBRIE</t>
+  </si>
+  <si>
+    <t>LUCIA GLADYS RIVEROS</t>
+  </si>
+  <si>
+    <t>SILVINA ELEANA TORRES QUIROGA</t>
+  </si>
+  <si>
+    <t>CLAUDIA CRISTINA BECERRA</t>
+  </si>
+  <si>
+    <t>ADRIANA NICOLASA HERRERA</t>
+  </si>
+  <si>
+    <t>JUAN DOMINGO NARVAEZ SOSA</t>
+  </si>
+  <si>
+    <t>ROBERTO ESTEBAN RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ELSA MARCELA ZARATE</t>
+  </si>
+  <si>
+    <t>NESTOR DARIO PERALTA</t>
+  </si>
+  <si>
+    <t>MARCELO DANIEL GOMEZ</t>
   </si>
 </sst>
 </file>
@@ -354,8 +2022,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -370,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>23977476</v>
+        <v>20132210</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -378,7 +2049,4535 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1231232</v>
+        <v>21798869</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>22084337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>22705868</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>23378916</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>23943839</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23977299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>23977620</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>25167599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>25195881</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>25859978</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>25939029</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>27042420</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>27042420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>28727999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>29176353</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>30508374</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>31199344</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>31400725</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>34194023</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>35508892</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>35848622</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>35924298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>37462200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>37832746</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>37833125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>38218466</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>25252710</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>39791082</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>28020824</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>23545573</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>21609611</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>20801544</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>28020762</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>28218709</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>22958653</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>25550950</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>27350286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>35510192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>20275797</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>25823510</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>35851442</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>23283670</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>22663948</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>21360557</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>31637248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>35192536</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>36423367</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>27042984</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>27350254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>22754992</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>40779942</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>32689953</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>29540715</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>24234042</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>28005398</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>20302348</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>20132758</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>16865408</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>31125607</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>22227351</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>33759050</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>31510714</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>18206980</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>16527057</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>32807457</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>22291471</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>33809478</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>17032494</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>30688445</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>35509995</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>22291473</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>22658265</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>35509542</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>30091185</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>35509463</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>35192508</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>37833586</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>34351341</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>25319611</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>26287050</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>30092401</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>35318149</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>17457982</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>38593464</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>21358734</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>23545157</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>40592203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>21362864</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>41297334</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>30483403</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>34916387</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>25550783</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>26511632</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>39994929</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>17738324</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>25167378</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>28727921</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>16859035</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>36254820</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>25549295</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>25549295</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>29861634</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>22754831</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>21360196</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>27685434</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>33336239</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>24234281</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>31366333</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>28855990</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>39524184</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>29996746</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>35924747</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>20444595</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>23633954</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>35507573</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>35505677</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>26434853</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>35735309</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>34920250</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>25823743</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>39425046</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>20302396</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>22658323</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>33475056</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>33185636</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>39791757</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>35924093</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>25649661</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>25939650</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>28005105</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>32679850</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>21611539</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>22289923</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>18611374</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>34698346</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>23331973</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>21359902</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>31901229</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>35922404</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>38075999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>25939858</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>23922370</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>27784738</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>26790157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>33759067</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>25573723</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>33095643</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>31714686</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>31870959</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>17417676</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>26656326</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>27574134</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>152</v>
+      </c>
+      <c r="B155">
+        <v>27574134</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>153</v>
+      </c>
+      <c r="B156">
+        <v>21362554</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>154</v>
+      </c>
+      <c r="B157">
+        <v>23638442</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>155</v>
+      </c>
+      <c r="B158">
+        <v>22998153</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>156</v>
+      </c>
+      <c r="B159">
+        <v>29621476</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>157</v>
+      </c>
+      <c r="B160">
+        <v>39008392</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>158</v>
+      </c>
+      <c r="B161">
+        <v>20675417</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>159</v>
+      </c>
+      <c r="B162">
+        <v>31871041</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>160</v>
+      </c>
+      <c r="B163">
+        <v>23735367</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>161</v>
+      </c>
+      <c r="B164">
+        <v>29481326</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>162</v>
+      </c>
+      <c r="B165">
+        <v>31005291</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>163</v>
+      </c>
+      <c r="B166">
+        <v>35192564</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>164</v>
+      </c>
+      <c r="B167">
+        <v>31643110</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>165</v>
+      </c>
+      <c r="B168">
+        <v>35734764</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>166</v>
+      </c>
+      <c r="B169">
+        <v>20132563</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>167</v>
+      </c>
+      <c r="B170">
+        <v>34351400</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>168</v>
+      </c>
+      <c r="B171">
+        <v>30839386</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>169</v>
+      </c>
+      <c r="B172">
+        <v>30738205</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>170</v>
+      </c>
+      <c r="B173">
+        <v>42237389</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>171</v>
+      </c>
+      <c r="B174">
+        <v>21994021</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>172</v>
+      </c>
+      <c r="B175">
+        <v>25319299</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>173</v>
+      </c>
+      <c r="B176">
+        <v>43376191</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>174</v>
+      </c>
+      <c r="B177">
+        <v>29707486</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>175</v>
+      </c>
+      <c r="B178">
+        <v>22011935</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>176</v>
+      </c>
+      <c r="B179">
+        <v>21357889</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>177</v>
+      </c>
+      <c r="B180">
+        <v>32808052</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>178</v>
+      </c>
+      <c r="B181">
+        <v>29557893</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>179</v>
+      </c>
+      <c r="B182">
+        <v>39955412</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>180</v>
+      </c>
+      <c r="B183">
+        <v>39651475</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>181</v>
+      </c>
+      <c r="B184">
+        <v>34920112</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>30</v>
+      </c>
+      <c r="B185">
+        <v>28020824</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>182</v>
+      </c>
+      <c r="B186">
+        <v>34062068</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>183</v>
+      </c>
+      <c r="B187">
+        <v>25573629</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>184</v>
+      </c>
+      <c r="B188">
+        <v>30346195</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>185</v>
+      </c>
+      <c r="B189">
+        <v>44060927</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>186</v>
+      </c>
+      <c r="B190">
+        <v>21876781</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>187</v>
+      </c>
+      <c r="B191">
+        <v>16666847</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>188</v>
+      </c>
+      <c r="B192">
+        <v>23979668</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>189</v>
+      </c>
+      <c r="B193">
+        <v>28659064</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>190</v>
+      </c>
+      <c r="B194">
+        <v>21362923</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>191</v>
+      </c>
+      <c r="B195">
+        <v>23381673</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>192</v>
+      </c>
+      <c r="B196">
+        <v>32878331</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>193</v>
+      </c>
+      <c r="B197">
+        <v>25195454</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>194</v>
+      </c>
+      <c r="B198">
+        <v>24038718</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>195</v>
+      </c>
+      <c r="B199">
+        <v>30634951</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>196</v>
+      </c>
+      <c r="B200">
+        <v>26510702</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>197</v>
+      </c>
+      <c r="B201">
+        <v>31621570</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>198</v>
+      </c>
+      <c r="B202">
+        <v>35922831</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>199</v>
+      </c>
+      <c r="B203">
+        <v>18515039</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>200</v>
+      </c>
+      <c r="B204">
+        <v>25573235</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>201</v>
+      </c>
+      <c r="B205">
+        <v>42005643</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>202</v>
+      </c>
+      <c r="B206">
+        <v>29889175</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>203</v>
+      </c>
+      <c r="B207">
+        <v>39011528</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>204</v>
+      </c>
+      <c r="B208">
+        <v>22958834</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>205</v>
+      </c>
+      <c r="B209">
+        <v>36544304</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>206</v>
+      </c>
+      <c r="B210">
+        <v>20366669</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>207</v>
+      </c>
+      <c r="B211">
+        <v>33289499</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>208</v>
+      </c>
+      <c r="B212">
+        <v>30708819</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>209</v>
+      </c>
+      <c r="B213">
+        <v>27042891</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>210</v>
+      </c>
+      <c r="B214">
+        <v>27350674</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>211</v>
+      </c>
+      <c r="B215">
+        <v>24836541</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>212</v>
+      </c>
+      <c r="B216">
+        <v>39008469</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>213</v>
+      </c>
+      <c r="B217">
+        <v>26790933</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>214</v>
+      </c>
+      <c r="B218">
+        <v>38217770</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>215</v>
+      </c>
+      <c r="B219">
+        <v>43078102</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>216</v>
+      </c>
+      <c r="B220">
+        <v>32168127</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>217</v>
+      </c>
+      <c r="B221">
+        <v>28538571</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>218</v>
+      </c>
+      <c r="B222">
+        <v>32939171</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>219</v>
+      </c>
+      <c r="B223">
+        <v>28243817</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>220</v>
+      </c>
+      <c r="B224">
+        <v>35318328</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>221</v>
+      </c>
+      <c r="B225">
+        <v>30891549</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>222</v>
+      </c>
+      <c r="B226">
+        <v>34054470</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>223</v>
+      </c>
+      <c r="B227">
+        <v>35506419</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>224</v>
+      </c>
+      <c r="B228">
+        <v>27043082</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>225</v>
+      </c>
+      <c r="B229">
+        <v>31237713</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>226</v>
+      </c>
+      <c r="B230">
+        <v>28706069</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>227</v>
+      </c>
+      <c r="B231">
+        <v>38016176</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>228</v>
+      </c>
+      <c r="B232">
+        <v>33438493</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>229</v>
+      </c>
+      <c r="B233">
+        <v>33848792</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>230</v>
+      </c>
+      <c r="B234">
+        <v>39425240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>231</v>
+      </c>
+      <c r="B235">
+        <v>37647794</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>232</v>
+      </c>
+      <c r="B236">
+        <v>34875811</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>233</v>
+      </c>
+      <c r="B237">
+        <v>26288503</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>234</v>
+      </c>
+      <c r="B238">
+        <v>22705706</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>235</v>
+      </c>
+      <c r="B239">
+        <v>36586312</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>235</v>
+      </c>
+      <c r="B240">
+        <v>36586312</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>236</v>
+      </c>
+      <c r="B241">
+        <v>27574328</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>237</v>
+      </c>
+      <c r="B242">
+        <v>36033777</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>238</v>
+      </c>
+      <c r="B243">
+        <v>24607062</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>239</v>
+      </c>
+      <c r="B244">
+        <v>29943010</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>240</v>
+      </c>
+      <c r="B245">
+        <v>34916206</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>241</v>
+      </c>
+      <c r="B246">
+        <v>34920543</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>242</v>
+      </c>
+      <c r="B247">
+        <v>29165891</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>243</v>
+      </c>
+      <c r="B248">
+        <v>21609942</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>244</v>
+      </c>
+      <c r="B249">
+        <v>38078477</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>245</v>
+      </c>
+      <c r="B250">
+        <v>31454777</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>246</v>
+      </c>
+      <c r="B251">
+        <v>22465998</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>247</v>
+      </c>
+      <c r="B252">
+        <v>32447299</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>248</v>
+      </c>
+      <c r="B253">
+        <v>39425539</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>249</v>
+      </c>
+      <c r="B254">
+        <v>22063989</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>250</v>
+      </c>
+      <c r="B255">
+        <v>33629420</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>251</v>
+      </c>
+      <c r="B256">
+        <v>39791756</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>252</v>
+      </c>
+      <c r="B257">
+        <v>22705583</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>252</v>
+      </c>
+      <c r="B258">
+        <v>22705583</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>253</v>
+      </c>
+      <c r="B259">
+        <v>36034327</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>254</v>
+      </c>
+      <c r="B260">
+        <v>35850825</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>255</v>
+      </c>
+      <c r="B261">
+        <v>34195208</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>256</v>
+      </c>
+      <c r="B262">
+        <v>34696608</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>257</v>
+      </c>
+      <c r="B263">
+        <v>32140370</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>258</v>
+      </c>
+      <c r="B264">
+        <v>34193946</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>259</v>
+      </c>
+      <c r="B265">
+        <v>34333548</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>260</v>
+      </c>
+      <c r="B266">
+        <v>35924319</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>261</v>
+      </c>
+      <c r="B267">
+        <v>17243933</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>262</v>
+      </c>
+      <c r="B268">
+        <v>30145591</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>263</v>
+      </c>
+      <c r="B269">
+        <v>33839091</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>264</v>
+      </c>
+      <c r="B270">
+        <v>25299276</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>265</v>
+      </c>
+      <c r="B271">
+        <v>43085500</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>266</v>
+      </c>
+      <c r="B272">
+        <v>34430098</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>267</v>
+      </c>
+      <c r="B273">
+        <v>37648862</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>268</v>
+      </c>
+      <c r="B274">
+        <v>23735296</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>269</v>
+      </c>
+      <c r="B275">
+        <v>39182690</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>270</v>
+      </c>
+      <c r="B276">
+        <v>38591347</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>271</v>
+      </c>
+      <c r="B277">
+        <v>25823117</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>272</v>
+      </c>
+      <c r="B278">
+        <v>39653288</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>273</v>
+      </c>
+      <c r="B279">
+        <v>29426738</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>274</v>
+      </c>
+      <c r="B280">
+        <v>40265466</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>275</v>
+      </c>
+      <c r="B281">
+        <v>22358736</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>276</v>
+      </c>
+      <c r="B282">
+        <v>35923355</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>277</v>
+      </c>
+      <c r="B283">
+        <v>21520574</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>278</v>
+      </c>
+      <c r="B284">
+        <v>24244588</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>279</v>
+      </c>
+      <c r="B285">
+        <v>32808208</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>280</v>
+      </c>
+      <c r="B286">
+        <v>34194496</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>281</v>
+      </c>
+      <c r="B287">
+        <v>22227467</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>282</v>
+      </c>
+      <c r="B288">
+        <v>30688129</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>283</v>
+      </c>
+      <c r="B289">
+        <v>29608614</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>284</v>
+      </c>
+      <c r="B290">
+        <v>22011971</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>285</v>
+      </c>
+      <c r="B291">
+        <v>31400571</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>286</v>
+      </c>
+      <c r="B292">
+        <v>34696606</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>287</v>
+      </c>
+      <c r="B293">
+        <v>30335305</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>288</v>
+      </c>
+      <c r="B294">
+        <v>40995577</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>289</v>
+      </c>
+      <c r="B295">
+        <v>38217325</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>290</v>
+      </c>
+      <c r="B296">
+        <v>23046816</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>291</v>
+      </c>
+      <c r="B297">
+        <v>17925934</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>292</v>
+      </c>
+      <c r="B298">
+        <v>23545491</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>293</v>
+      </c>
+      <c r="B299">
+        <v>30157633</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>294</v>
+      </c>
+      <c r="B300">
+        <v>27350271</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>295</v>
+      </c>
+      <c r="B301">
+        <v>32454701</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>296</v>
+      </c>
+      <c r="B302">
+        <v>30840436</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>297</v>
+      </c>
+      <c r="B303">
+        <v>31214242</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>298</v>
+      </c>
+      <c r="B304">
+        <v>18762856</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>299</v>
+      </c>
+      <c r="B305">
+        <v>33095365</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>300</v>
+      </c>
+      <c r="B306">
+        <v>37297222</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>301</v>
+      </c>
+      <c r="B307">
+        <v>38015584</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>302</v>
+      </c>
+      <c r="B308">
+        <v>34407240</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>303</v>
+      </c>
+      <c r="B309">
+        <v>31633082</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>304</v>
+      </c>
+      <c r="B310">
+        <v>21592141</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>305</v>
+      </c>
+      <c r="B311">
+        <v>31005212</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>306</v>
+      </c>
+      <c r="B312">
+        <v>36251543</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>307</v>
+      </c>
+      <c r="B313">
+        <v>26678659</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>308</v>
+      </c>
+      <c r="B314">
+        <v>24786626</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>309</v>
+      </c>
+      <c r="B315">
+        <v>20943353</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>310</v>
+      </c>
+      <c r="B316">
+        <v>33025782</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>311</v>
+      </c>
+      <c r="B317">
+        <v>41814281</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>312</v>
+      </c>
+      <c r="B318">
+        <v>25319660</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>313</v>
+      </c>
+      <c r="B319">
+        <v>32083746</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>314</v>
+      </c>
+      <c r="B320">
+        <v>38929909</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>315</v>
+      </c>
+      <c r="B321">
+        <v>30246740</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>316</v>
+      </c>
+      <c r="B322">
+        <v>24971822</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>317</v>
+      </c>
+      <c r="B323">
+        <v>18412180</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>318</v>
+      </c>
+      <c r="B324">
+        <v>36031917</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>319</v>
+      </c>
+      <c r="B325">
+        <v>42990241</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>320</v>
+      </c>
+      <c r="B326">
+        <v>20462170</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>321</v>
+      </c>
+      <c r="B327">
+        <v>21610055</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>322</v>
+      </c>
+      <c r="B328">
+        <v>26511869</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>323</v>
+      </c>
+      <c r="B329">
+        <v>27350672</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>324</v>
+      </c>
+      <c r="B330">
+        <v>36033428</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>325</v>
+      </c>
+      <c r="B331">
+        <v>38461798</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>326</v>
+      </c>
+      <c r="B332">
+        <v>26511704</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>327</v>
+      </c>
+      <c r="B333">
+        <v>28262965</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>149</v>
+      </c>
+      <c r="B334">
+        <v>31870959</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>328</v>
+      </c>
+      <c r="B335">
+        <v>17051672</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>329</v>
+      </c>
+      <c r="B336">
+        <v>36252633</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>330</v>
+      </c>
+      <c r="B337">
+        <v>35851226</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>331</v>
+      </c>
+      <c r="B338">
+        <v>25319759</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>332</v>
+      </c>
+      <c r="B339">
+        <v>22815241</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>333</v>
+      </c>
+      <c r="B340">
+        <v>26511702</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>334</v>
+      </c>
+      <c r="B341">
+        <v>20935932</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>335</v>
+      </c>
+      <c r="B342">
+        <v>21926852</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>336</v>
+      </c>
+      <c r="B343">
+        <v>28218821</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>337</v>
+      </c>
+      <c r="B344">
+        <v>43186293</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>156</v>
+      </c>
+      <c r="B345">
+        <v>29621476</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>338</v>
+      </c>
+      <c r="B346">
+        <v>28773603</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>339</v>
+      </c>
+      <c r="B347">
+        <v>21360110</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>340</v>
+      </c>
+      <c r="B348">
+        <v>24724120</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>341</v>
+      </c>
+      <c r="B349">
+        <v>25938221</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>342</v>
+      </c>
+      <c r="B350">
+        <v>32214496</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>343</v>
+      </c>
+      <c r="B351">
+        <v>21611898</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>344</v>
+      </c>
+      <c r="B352">
+        <v>36031913</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>345</v>
+      </c>
+      <c r="B353">
+        <v>32750298</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>165</v>
+      </c>
+      <c r="B354">
+        <v>35734764</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>346</v>
+      </c>
+      <c r="B355">
+        <v>23378792</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>347</v>
+      </c>
+      <c r="B356">
+        <v>33232443</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>348</v>
+      </c>
+      <c r="B357">
+        <v>28040876</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>349</v>
+      </c>
+      <c r="B358">
+        <v>39011214</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>350</v>
+      </c>
+      <c r="B359">
+        <v>24713552</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>351</v>
+      </c>
+      <c r="B360">
+        <v>27043358</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>352</v>
+      </c>
+      <c r="B361">
+        <v>28982583</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>353</v>
+      </c>
+      <c r="B362">
+        <v>30694903</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>354</v>
+      </c>
+      <c r="B363">
+        <v>31401396</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>355</v>
+      </c>
+      <c r="B364">
+        <v>33058706</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>356</v>
+      </c>
+      <c r="B365">
+        <v>33234914</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>357</v>
+      </c>
+      <c r="B366">
+        <v>34660397</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>358</v>
+      </c>
+      <c r="B367">
+        <v>34917402</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>359</v>
+      </c>
+      <c r="B368">
+        <v>36032532</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>360</v>
+      </c>
+      <c r="B369">
+        <v>36034054</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>361</v>
+      </c>
+      <c r="B370">
+        <v>43838325</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>362</v>
+      </c>
+      <c r="B371">
+        <v>46984847</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>363</v>
+      </c>
+      <c r="B372">
+        <v>47239184</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>364</v>
+      </c>
+      <c r="B373">
+        <v>47239192</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>365</v>
+      </c>
+      <c r="B374">
+        <v>47287964</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>366</v>
+      </c>
+      <c r="B375">
+        <v>47625821</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>367</v>
+      </c>
+      <c r="B376">
+        <v>47625824</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>368</v>
+      </c>
+      <c r="B377">
+        <v>47927626</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>369</v>
+      </c>
+      <c r="B378">
+        <v>47927645</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>370</v>
+      </c>
+      <c r="B379">
+        <v>47927647</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>371</v>
+      </c>
+      <c r="B380">
+        <v>47927657</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>372</v>
+      </c>
+      <c r="B381">
+        <v>47927668</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>373</v>
+      </c>
+      <c r="B382">
+        <v>47927685</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>374</v>
+      </c>
+      <c r="B383">
+        <v>47927694</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>375</v>
+      </c>
+      <c r="B384">
+        <v>48014646</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>376</v>
+      </c>
+      <c r="B385">
+        <v>49101412</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>377</v>
+      </c>
+      <c r="B386">
+        <v>49229245</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>378</v>
+      </c>
+      <c r="B387">
+        <v>49281032</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>379</v>
+      </c>
+      <c r="B388">
+        <v>49285408</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>380</v>
+      </c>
+      <c r="B389">
+        <v>39008659</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>381</v>
+      </c>
+      <c r="B390">
+        <v>37646561</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>382</v>
+      </c>
+      <c r="B391">
+        <v>32572840</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>383</v>
+      </c>
+      <c r="B392">
+        <v>40264707</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>384</v>
+      </c>
+      <c r="B393">
+        <v>35508640</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>385</v>
+      </c>
+      <c r="B394">
+        <v>35850196</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>386</v>
+      </c>
+      <c r="B395">
+        <v>35850358</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>387</v>
+      </c>
+      <c r="B396">
+        <v>28717807</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>388</v>
+      </c>
+      <c r="B397">
+        <v>33289960</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>389</v>
+      </c>
+      <c r="B398">
+        <v>29102523</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>390</v>
+      </c>
+      <c r="B399">
+        <v>26441594</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>391</v>
+      </c>
+      <c r="B400">
+        <v>34921258</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>392</v>
+      </c>
+      <c r="B401">
+        <v>32084257</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>393</v>
+      </c>
+      <c r="B402">
+        <v>38074823</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>394</v>
+      </c>
+      <c r="B403">
+        <v>39954926</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>395</v>
+      </c>
+      <c r="B404">
+        <v>22496570</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>396</v>
+      </c>
+      <c r="B405">
+        <v>27764110</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>397</v>
+      </c>
+      <c r="B406">
+        <v>36254959</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>398</v>
+      </c>
+      <c r="B407">
+        <v>20548089</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>399</v>
+      </c>
+      <c r="B408">
+        <v>33836894</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>400</v>
+      </c>
+      <c r="B409">
+        <v>31401261</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>401</v>
+      </c>
+      <c r="B410">
+        <v>25714469</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>402</v>
+      </c>
+      <c r="B411">
+        <v>22659907</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>403</v>
+      </c>
+      <c r="B412">
+        <v>28675403</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>404</v>
+      </c>
+      <c r="B413">
+        <v>22535503</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>405</v>
+      </c>
+      <c r="B414">
+        <v>23635064</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>406</v>
+      </c>
+      <c r="B415">
+        <v>39996113</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>407</v>
+      </c>
+      <c r="B416">
+        <v>32116442</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>408</v>
+      </c>
+      <c r="B417">
+        <v>39995950</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>409</v>
+      </c>
+      <c r="B418">
+        <v>37634969</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>410</v>
+      </c>
+      <c r="B419">
+        <v>37741563</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>411</v>
+      </c>
+      <c r="B420">
+        <v>31738447</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>412</v>
+      </c>
+      <c r="B421">
+        <v>28192629</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>413</v>
+      </c>
+      <c r="B422">
+        <v>32724118</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>414</v>
+      </c>
+      <c r="B423">
+        <v>33672527</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>415</v>
+      </c>
+      <c r="B424">
+        <v>22438183</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>416</v>
+      </c>
+      <c r="B425">
+        <v>28020824</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>417</v>
+      </c>
+      <c r="B426">
+        <v>42163243</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>418</v>
+      </c>
+      <c r="B427">
+        <v>30989289</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>419</v>
+      </c>
+      <c r="B428">
+        <v>30376779</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>420</v>
+      </c>
+      <c r="B429">
+        <v>24234816</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>421</v>
+      </c>
+      <c r="B430">
+        <v>35192536</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>422</v>
+      </c>
+      <c r="B431">
+        <v>39008761</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>423</v>
+      </c>
+      <c r="B432">
+        <v>38462658</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>424</v>
+      </c>
+      <c r="B433">
+        <v>32454797</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>425</v>
+      </c>
+      <c r="B434">
+        <v>36034801</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>426</v>
+      </c>
+      <c r="B435">
+        <v>35509968</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>427</v>
+      </c>
+      <c r="B436">
+        <v>24793316</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>428</v>
+      </c>
+      <c r="B437">
+        <v>22159068</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>429</v>
+      </c>
+      <c r="B438">
+        <v>35923618</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>430</v>
+      </c>
+      <c r="B439">
+        <v>33825730</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>431</v>
+      </c>
+      <c r="B440">
+        <v>37641172</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>432</v>
+      </c>
+      <c r="B441">
+        <v>36033203</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>433</v>
+      </c>
+      <c r="B442">
+        <v>35197321</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>434</v>
+      </c>
+      <c r="B443">
+        <v>36251265</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>435</v>
+      </c>
+      <c r="B444">
+        <v>43281404</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>436</v>
+      </c>
+      <c r="B445">
+        <v>30631712</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>437</v>
+      </c>
+      <c r="B446">
+        <v>46407684</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>438</v>
+      </c>
+      <c r="B447">
+        <v>37507037</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>439</v>
+      </c>
+      <c r="B448">
+        <v>23633954</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>440</v>
+      </c>
+      <c r="B449">
+        <v>35849305</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>441</v>
+      </c>
+      <c r="B450">
+        <v>38593960</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>442</v>
+      </c>
+      <c r="B451">
+        <v>29351537</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>443</v>
+      </c>
+      <c r="B452">
+        <v>22760648</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>444</v>
+      </c>
+      <c r="B453">
+        <v>38076556</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>445</v>
+      </c>
+      <c r="B454">
+        <v>21357510</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>446</v>
+      </c>
+      <c r="B455">
+        <v>26288312</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>447</v>
+      </c>
+      <c r="B456">
+        <v>28388005</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>448</v>
+      </c>
+      <c r="B457">
+        <v>23735616</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>449</v>
+      </c>
+      <c r="B458">
+        <v>23098959</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>450</v>
+      </c>
+      <c r="B459">
+        <v>36250340</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>451</v>
+      </c>
+      <c r="B460">
+        <v>38461503</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>452</v>
+      </c>
+      <c r="B461">
+        <v>27923000</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>453</v>
+      </c>
+      <c r="B462">
+        <v>37297313</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>454</v>
+      </c>
+      <c r="B463">
+        <v>35852312</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>455</v>
+      </c>
+      <c r="B464">
+        <v>40711266</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>456</v>
+      </c>
+      <c r="B465">
+        <v>25939784</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>457</v>
+      </c>
+      <c r="B466">
+        <v>20133399</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>458</v>
+      </c>
+      <c r="B467">
+        <v>35849446</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>459</v>
+      </c>
+      <c r="B468">
+        <v>20463316</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>460</v>
+      </c>
+      <c r="B469">
+        <v>30246621</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>461</v>
+      </c>
+      <c r="B470">
+        <v>32446950</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>462</v>
+      </c>
+      <c r="B471">
+        <v>22741199</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>463</v>
+      </c>
+      <c r="B472">
+        <v>22815170</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>464</v>
+      </c>
+      <c r="B473">
+        <v>33759315</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>465</v>
+      </c>
+      <c r="B474">
+        <v>26287004</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>466</v>
+      </c>
+      <c r="B475">
+        <v>46071067</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>467</v>
+      </c>
+      <c r="B476">
+        <v>24091734</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>468</v>
+      </c>
+      <c r="B477">
+        <v>39007476</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>469</v>
+      </c>
+      <c r="B478">
+        <v>35734606</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>470</v>
+      </c>
+      <c r="B479">
+        <v>25167793</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>471</v>
+      </c>
+      <c r="B480">
+        <v>22064928</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>472</v>
+      </c>
+      <c r="B481">
+        <v>34917456</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>473</v>
+      </c>
+      <c r="B482">
+        <v>36669464</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>474</v>
+      </c>
+      <c r="B483">
+        <v>22998153</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>475</v>
+      </c>
+      <c r="B484">
+        <v>28040497</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>476</v>
+      </c>
+      <c r="B485">
+        <v>34414009</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>477</v>
+      </c>
+      <c r="B486">
+        <v>30130091</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>478</v>
+      </c>
+      <c r="B487">
+        <v>39653093</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>479</v>
+      </c>
+      <c r="B488">
+        <v>27043929</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>480</v>
+      </c>
+      <c r="B489">
+        <v>20130022</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>481</v>
+      </c>
+      <c r="B490">
+        <v>42712345</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>482</v>
+      </c>
+      <c r="B491">
+        <v>43157691</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>483</v>
+      </c>
+      <c r="B492">
+        <v>21360357</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>484</v>
+      </c>
+      <c r="B493">
+        <v>40593552</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>485</v>
+      </c>
+      <c r="B494">
+        <v>37647740</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>486</v>
+      </c>
+      <c r="B495">
+        <v>40728902</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>487</v>
+      </c>
+      <c r="B496">
+        <v>21741808</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>488</v>
+      </c>
+      <c r="B497">
+        <v>38078463</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>489</v>
+      </c>
+      <c r="B498">
+        <v>38591731</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>490</v>
+      </c>
+      <c r="B499">
+        <v>35848733</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>491</v>
+      </c>
+      <c r="B500">
+        <v>29935752</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>492</v>
+      </c>
+      <c r="B501">
+        <v>35736020</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>493</v>
+      </c>
+      <c r="B502">
+        <v>40265000</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>494</v>
+      </c>
+      <c r="B503">
+        <v>31643199</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>495</v>
+      </c>
+      <c r="B504">
+        <v>21823212</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>496</v>
+      </c>
+      <c r="B505">
+        <v>25167277</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>497</v>
+      </c>
+      <c r="B506">
+        <v>39010514</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>498</v>
+      </c>
+      <c r="B507">
+        <v>25118277</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>499</v>
+      </c>
+      <c r="B508">
+        <v>35506096</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>500</v>
+      </c>
+      <c r="B509">
+        <v>23498166</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>501</v>
+      </c>
+      <c r="B510">
+        <v>40367812</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>502</v>
+      </c>
+      <c r="B511">
+        <v>23381583</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>503</v>
+      </c>
+      <c r="B512">
+        <v>39425498</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>504</v>
+      </c>
+      <c r="B513">
+        <v>24331443</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>505</v>
+      </c>
+      <c r="B514">
+        <v>43280889</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>506</v>
+      </c>
+      <c r="B515">
+        <v>42918238</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>507</v>
+      </c>
+      <c r="B516">
+        <v>25995498</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>508</v>
+      </c>
+      <c r="B517">
+        <v>31324294</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>509</v>
+      </c>
+      <c r="B518">
+        <v>24660300</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>510</v>
+      </c>
+      <c r="B519">
+        <v>33630175</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>511</v>
+      </c>
+      <c r="B520">
+        <v>20953172</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>512</v>
+      </c>
+      <c r="B521">
+        <v>23071397</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>513</v>
+      </c>
+      <c r="B522">
+        <v>26511248</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>514</v>
+      </c>
+      <c r="B523">
+        <v>35509040</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>515</v>
+      </c>
+      <c r="B524">
+        <v>22959630</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>516</v>
+      </c>
+      <c r="B525">
+        <v>28691728</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>517</v>
+      </c>
+      <c r="B526">
+        <v>17180676</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>518</v>
+      </c>
+      <c r="B527">
+        <v>41054513</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>519</v>
+      </c>
+      <c r="B528">
+        <v>33846211</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>520</v>
+      </c>
+      <c r="B529">
+        <v>17314245</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>521</v>
+      </c>
+      <c r="B530">
+        <v>28218810</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>522</v>
+      </c>
+      <c r="B531">
+        <v>25104021</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>523</v>
+      </c>
+      <c r="B532">
+        <v>26510108</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>524</v>
+      </c>
+      <c r="B533">
+        <v>25550634</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>525</v>
+      </c>
+      <c r="B534">
+        <v>38078712</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>526</v>
+      </c>
+      <c r="B535">
+        <v>18400215</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>527</v>
+      </c>
+      <c r="B536">
+        <v>20560516</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>528</v>
+      </c>
+      <c r="B537">
+        <v>24331329</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>529</v>
+      </c>
+      <c r="B538">
+        <v>30242428</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>530</v>
+      </c>
+      <c r="B539">
+        <v>24735080</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>531</v>
+      </c>
+      <c r="B540">
+        <v>32807858</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>532</v>
+      </c>
+      <c r="B541">
+        <v>30508360</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>533</v>
+      </c>
+      <c r="B542">
+        <v>25135479</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>534</v>
+      </c>
+      <c r="B543">
+        <v>35736711</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>535</v>
+      </c>
+      <c r="B544">
+        <v>39183944</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>536</v>
+      </c>
+      <c r="B545">
+        <v>20560556</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>537</v>
+      </c>
+      <c r="B546">
+        <v>33429694</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>538</v>
+      </c>
+      <c r="B547">
+        <v>31869167</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>539</v>
+      </c>
+      <c r="B548">
+        <v>34696787</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>540</v>
+      </c>
+      <c r="B549">
+        <v>26511680</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>541</v>
+      </c>
+      <c r="B550">
+        <v>17314232</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>542</v>
+      </c>
+      <c r="B551">
+        <v>27784830</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>543</v>
+      </c>
+      <c r="B552">
+        <v>35849088</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>544</v>
+      </c>
+      <c r="B553">
+        <v>26434925</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>545</v>
+      </c>
+      <c r="B554">
+        <v>24879246</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>546</v>
+      </c>
+      <c r="B555">
+        <v>41909067</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>420</v>
+      </c>
+      <c r="B556">
+        <v>24234816</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>547</v>
+      </c>
+      <c r="B557">
+        <v>22358400</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>548</v>
+      </c>
+      <c r="B558">
+        <v>39651346</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>549</v>
+      </c>
+      <c r="B559">
+        <v>26593067</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>550</v>
+      </c>
+      <c r="B560">
+        <v>29313351</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>551</v>
+      </c>
+      <c r="B561">
+        <v>17548401</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>552</v>
+      </c>
+      <c r="B562">
+        <v>35149533</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>553</v>
+      </c>
+      <c r="B563">
+        <v>27685162</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>554</v>
+      </c>
+      <c r="B564">
+        <v>20131266</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>555</v>
+      </c>
+      <c r="B565">
+        <v>25991648</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>556</v>
+      </c>
+      <c r="B566">
+        <v>32807530</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>557</v>
+      </c>
+      <c r="B567">
+        <v>18510888</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>558</v>
+      </c>
+      <c r="B568">
+        <v>21360440</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>559</v>
+      </c>
+      <c r="B569">
+        <v>23977476</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\generador_certificados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CE7B6E-3918-4783-87F8-A45BC545EDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD288E0-4531-4686-98B8-6909E2E36CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="195" windowWidth="14160" windowHeight="15405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
